--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-30).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-30).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-166</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>R$ 818.432,44</t>
-  </si>
-  <si>
-    <t>R$ 4.623,91
-R$ 4.725,41</t>
-  </si>
-  <si>
-    <t>15.9%
-17.8%</t>
-  </si>
-  <si>
-    <t>49.9</t>
-  </si>
-  <si>
-    <t>5.5%</t>
-  </si>
-  <si>
-    <t>(93.7%)</t>
-  </si>
-  <si>
-    <t>(146.1%)</t>
+171</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R$ 834.846,37</t>
+  </si>
+  <si>
+    <t>R$ 4.587,07
+R$ 4.683,23</t>
+  </si>
+  <si>
+    <t>16.1%
+17.9%</t>
+  </si>
+  <si>
+    <t>49.5</t>
+  </si>
+  <si>
+    <t>5.4%</t>
+  </si>
+  <si>
+    <t>(70.0%)</t>
+  </si>
+  <si>
+    <t>(122.1%)</t>
   </si>
   <si>
     <t>4.3%</t>
@@ -947,10 +947,10 @@
     <t>1.0%</t>
   </si>
   <si>
-    <t>27.6</t>
-  </si>
-  <si>
-    <t>71.5%</t>
+    <t>27.8</t>
+  </si>
+  <si>
+    <t>71.3%</t>
   </si>
   <si>
     <t>11.6%</t>
@@ -959,19 +959,19 @@
     <t>5.1</t>
   </si>
   <si>
-    <t>7.4</t>
-  </si>
-  <si>
-    <t>12.1</t>
-  </si>
-  <si>
-    <t>19.3</t>
-  </si>
-  <si>
-    <t>69.9%</t>
-  </si>
-  <si>
-    <t>-R$ 20.428,33</t>
+    <t>7.5</t>
+  </si>
+  <si>
+    <t>12.5</t>
+  </si>
+  <si>
+    <t>19.4</t>
+  </si>
+  <si>
+    <t>69.7%</t>
+  </si>
+  <si>
+    <t>-R$ 20.481,73</t>
   </si>
   <si>
     <t>2.94</t>
@@ -3025,7 +3025,9 @@
       <c r="AB13" s="8">
         <v>9.1833328124999998</v>
       </c>
-      <c r="AC13" s="8"/>
+      <c r="AC13" s="8">
+        <v>14.678124</v>
+      </c>
       <c r="AD13" s="8">
         <v>21.629948437500001</v>
       </c>
@@ -3285,7 +3287,9 @@
       <c r="AB15" s="8">
         <v>3.7673469387755101</v>
       </c>
-      <c r="AC15" s="8"/>
+      <c r="AC15" s="8">
+        <v>7.9534000000000002</v>
+      </c>
       <c r="AD15" s="8">
         <v>14.908163265306122</v>
       </c>
@@ -3807,7 +3811,9 @@
       <c r="AB19" s="8">
         <v>11.677351282051282</v>
       </c>
-      <c r="AC19" s="8"/>
+      <c r="AC19" s="8">
+        <v>17.83426</v>
+      </c>
       <c r="AD19" s="8">
         <v>24.4870825</v>
       </c>
@@ -4198,7 +4204,9 @@
       <c r="AB22" s="8">
         <v>13.798189130434782</v>
       </c>
-      <c r="AC22" s="8"/>
+      <c r="AC22" s="8">
+        <v>19.441303000000001</v>
+      </c>
       <c r="AD22" s="8">
         <v>26.367028260869564</v>
       </c>
@@ -4684,7 +4692,9 @@
       <c r="AB26" s="8">
         <v>10.607777333333333</v>
       </c>
-      <c r="AC26" s="8"/>
+      <c r="AC26" s="8">
+        <v>14.568383000000001</v>
+      </c>
       <c r="AD26" s="8">
         <v>21.118181818181817</v>
       </c>
@@ -5166,7 +5176,9 @@
       <c r="AB30" s="8">
         <v>14.512118181818181</v>
       </c>
-      <c r="AC30" s="8"/>
+      <c r="AC30" s="8">
+        <v>17.728787000000001</v>
+      </c>
       <c r="AD30" s="8">
         <v>24.896972727272725</v>
       </c>
@@ -5428,7 +5440,9 @@
       <c r="AB32" s="8">
         <v>4.7259881355932203</v>
       </c>
-      <c r="AC32" s="8"/>
+      <c r="AC32" s="8">
+        <v>7.2135579999999999</v>
+      </c>
       <c r="AD32" s="8">
         <v>13.181072881355933</v>
       </c>
@@ -5757,10 +5771,10 @@
         <v>-0.21875</v>
       </c>
       <c r="T35" s="6">
-        <v>-33.135632728229417</v>
+        <v>38.126595951623578</v>
       </c>
       <c r="U35" s="6">
-        <v>-35.232576913571393</v>
+        <v>36.029651766281603</v>
       </c>
       <c r="V35" s="6">
         <v>0.095763076702303232</v>
@@ -5838,7 +5852,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -5874,25 +5888,59 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
+      <c r="O36" s="5">
+        <v>3796.6300000000001</v>
+      </c>
+      <c r="P36" s="5">
+        <v>3796.6300000000001</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0.29893461243704844</v>
+      </c>
+      <c r="R36" s="7">
+        <v>40</v>
+      </c>
+      <c r="S36" s="6">
+        <v>0.14285714285714279</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.30932679771270838</v>
+      </c>
+      <c r="U36" s="6">
+        <v>-0.003579648267015748</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.14462259951588644</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.083010064188504012</v>
+      </c>
+      <c r="X36" s="8">
+        <v>62.642857142857146</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>8.0012500000000006</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>18.210604545454547</v>
+      </c>
       <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="AD36" s="8">
+        <v>29.900642307692308</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.35714285714285715</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -6269,7 +6317,9 @@
       <c r="AB39" s="8">
         <v>3.8041666666666667</v>
       </c>
-      <c r="AC39" s="8"/>
+      <c r="AC39" s="8">
+        <v>6.4420970000000004</v>
+      </c>
       <c r="AD39" s="8">
         <v>13.040231034482758</v>
       </c>
@@ -6582,7 +6632,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>44</v>
@@ -6618,25 +6668,61 @@
       <c t="s" r="N42" s="4">
         <v>52</v>
       </c>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
-      <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="6"/>
+      <c r="O42" s="5">
+        <v>3830.4200000000001</v>
+      </c>
+      <c r="P42" s="5">
+        <v>3830.4200000000001</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>0.35841093986055639</v>
+      </c>
+      <c r="R42" s="7">
+        <v>43</v>
+      </c>
+      <c r="S42" s="6">
+        <v>0.13157894736842102</v>
+      </c>
+      <c r="T42" s="6">
+        <v>0.31439317359454055</v>
+      </c>
+      <c r="U42" s="6">
+        <v>-0.019870431963074545</v>
+      </c>
+      <c r="V42" s="6">
+        <v>0.11758475571869403</v>
+      </c>
+      <c r="W42" s="6">
+        <v>0.064676719524229723</v>
+      </c>
+      <c r="X42" s="8">
+        <v>22.138270370370371</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>0.92592592592592593</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="8">
+        <v>5.0796756097560971</v>
+      </c>
+      <c r="AB42" s="8">
+        <v>4.1253320000000002</v>
+      </c>
+      <c r="AC42" s="8">
+        <v>9.2640229999999999</v>
+      </c>
+      <c r="AD42" s="8">
+        <v>15.623455555555555</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>1</v>
+      </c>
       <c r="AF42" s="9"/>
-      <c r="AG42" s="5"/>
+      <c r="AG42" s="5">
+        <v>0</v>
+      </c>
       <c r="AH42" s="10">
         <v>3</v>
       </c>
@@ -7404,7 +7490,9 @@
       <c r="AB48" s="8">
         <v>4.869522857142857</v>
       </c>
-      <c r="AC48" s="8"/>
+      <c r="AC48" s="8">
+        <v>11.741745</v>
+      </c>
       <c r="AD48" s="8">
         <v>17.880091666666669</v>
       </c>
@@ -7531,7 +7619,9 @@
       <c r="AB49" s="8">
         <v>11.97269574468085</v>
       </c>
-      <c r="AC49" s="8"/>
+      <c r="AC49" s="8">
+        <v>15.562150000000001</v>
+      </c>
       <c r="AD49" s="8">
         <v>22.558163265306121</v>
       </c>
@@ -7660,7 +7750,9 @@
       <c r="AB50" s="8">
         <v>8.8530999999999995</v>
       </c>
-      <c r="AC50" s="8"/>
+      <c r="AC50" s="8">
+        <v>12.089146</v>
+      </c>
       <c r="AD50" s="8">
         <v>19.318517777777778</v>
       </c>
@@ -7711,7 +7803,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7747,25 +7839,47 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
+      <c r="O51" s="5">
+        <v>286.80000000000001</v>
+      </c>
+      <c r="P51" s="5">
+        <v>286.80000000000001</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-0.71946710487704679</v>
+      </c>
+      <c r="R51" s="7">
+        <v>3</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.69999999999999996</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-1.0390167364016736</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.14348849372384939</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.30285041841004184</v>
+      </c>
       <c r="X51" s="8"/>
       <c r="Y51" s="6"/>
       <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
+      <c r="AA51" s="8">
+        <v>4.6027833333333339</v>
+      </c>
       <c r="AB51" s="8"/>
       <c r="AC51" s="8"/>
       <c r="AD51" s="8"/>
       <c r="AE51" s="6"/>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -8275,7 +8389,9 @@
       <c r="AB55" s="8">
         <v>9.5174603174603174</v>
       </c>
-      <c r="AC55" s="8"/>
+      <c r="AC55" s="8">
+        <v>13.540944</v>
+      </c>
       <c r="AD55" s="8">
         <v>20.517988888888887</v>
       </c>
@@ -8636,7 +8752,9 @@
       <c r="Z58" s="6"/>
       <c r="AA58" s="8"/>
       <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
+      <c r="AC58" s="8">
+        <v>11.227777</v>
+      </c>
       <c r="AD58" s="8"/>
       <c r="AE58" s="6"/>
       <c r="AF58" s="9"/>
@@ -9408,7 +9526,9 @@
       <c r="AB64" s="8">
         <v>10.086363636363636</v>
       </c>
-      <c r="AC64" s="8"/>
+      <c r="AC64" s="8">
+        <v>15.599406</v>
+      </c>
       <c r="AD64" s="8">
         <v>22.493181818181821</v>
       </c>
@@ -10279,7 +10399,9 @@
       <c r="AB71" s="8">
         <v>12.910869565217391</v>
       </c>
-      <c r="AC71" s="8"/>
+      <c r="AC71" s="8">
+        <v>15.594896</v>
+      </c>
       <c r="AD71" s="8">
         <v>22.940970833333335</v>
       </c>
@@ -10757,7 +10879,9 @@
       <c r="AB75" s="8">
         <v>10.891026923076923</v>
       </c>
-      <c r="AC75" s="8"/>
+      <c r="AC75" s="8">
+        <v>16.071794000000001</v>
+      </c>
       <c r="AD75" s="8">
         <v>23.01858846153846</v>
       </c>
@@ -10884,7 +11008,9 @@
       <c r="AB76" s="8">
         <v>15.226575675675674</v>
       </c>
-      <c r="AC76" s="8"/>
+      <c r="AC76" s="8">
+        <v>18.079226999999999</v>
+      </c>
       <c r="AD76" s="8">
         <v>24.18372093023256</v>
       </c>
@@ -11140,7 +11266,9 @@
       <c r="AB78" s="8">
         <v>4.4107516129032263</v>
       </c>
-      <c r="AC78" s="8"/>
+      <c r="AC78" s="8">
+        <v>6.8827949999999998</v>
+      </c>
       <c r="AD78" s="8">
         <v>14.850538709677419</v>
       </c>
@@ -11269,7 +11397,9 @@
       <c r="AB79" s="8">
         <v>11.615217391304347</v>
       </c>
-      <c r="AC79" s="8"/>
+      <c r="AC79" s="8">
+        <v>18.740911000000001</v>
+      </c>
       <c r="AD79" s="8">
         <v>25.82101304347826</v>
       </c>
@@ -11525,7 +11655,9 @@
       <c r="AB81" s="8">
         <v>13.532714814814815</v>
       </c>
-      <c r="AC81" s="8"/>
+      <c r="AC81" s="8">
+        <v>21.369752999999999</v>
+      </c>
       <c r="AD81" s="8">
         <v>28.322222222222223</v>
       </c>
@@ -12624,7 +12756,9 @@
       <c r="AB90" s="8">
         <v>20.815417500000002</v>
       </c>
-      <c r="AC90" s="8"/>
+      <c r="AC90" s="8">
+        <v>49.327916000000002</v>
+      </c>
       <c r="AD90" s="8">
         <v>56.217917499999999</v>
       </c>
@@ -13013,7 +13147,9 @@
       <c r="AB93" s="8">
         <v>2.2937163934426228</v>
       </c>
-      <c r="AC93" s="8"/>
+      <c r="AC93" s="8">
+        <v>4.5609279999999996</v>
+      </c>
       <c r="AD93" s="8">
         <v>11.503824590163934</v>
       </c>
@@ -13888,7 +14024,9 @@
       <c r="AB100" s="8">
         <v>5.6797086956521738</v>
       </c>
-      <c r="AC100" s="8"/>
+      <c r="AC100" s="8">
+        <v>9.3702889999999996</v>
+      </c>
       <c r="AD100" s="8">
         <v>18.315217391304348</v>
       </c>
@@ -14068,7 +14206,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>44</v>
@@ -14104,25 +14242,59 @@
       <c t="s" r="N102" s="4">
         <v>52</v>
       </c>
-      <c r="O102" s="5"/>
-      <c r="P102" s="5"/>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="7"/>
-      <c r="S102" s="6"/>
-      <c r="T102" s="6"/>
-      <c r="U102" s="6"/>
-      <c r="V102" s="6"/>
-      <c r="W102" s="6"/>
-      <c r="X102" s="8"/>
-      <c r="Y102" s="6"/>
-      <c r="Z102" s="6"/>
-      <c r="AA102" s="8"/>
-      <c r="AB102" s="8"/>
+      <c r="O102" s="5">
+        <v>3615.6500000000001</v>
+      </c>
+      <c r="P102" s="5">
+        <v>3615.6500000000001</v>
+      </c>
+      <c r="Q102" s="6">
+        <v>0.60721270958909002</v>
+      </c>
+      <c r="R102" s="7">
+        <v>30</v>
+      </c>
+      <c r="S102" s="6">
+        <v>0.071428571428571397</v>
+      </c>
+      <c r="T102" s="6">
+        <v>6.2174159556372988E-05</v>
+      </c>
+      <c r="U102" s="6">
+        <v>-0.33847999668109469</v>
+      </c>
+      <c r="V102" s="6">
+        <v>0.061795942638253151</v>
+      </c>
+      <c r="W102" s="6">
+        <v>0.039586934576078987</v>
+      </c>
+      <c r="X102" s="8">
+        <v>33.547499999999999</v>
+      </c>
+      <c r="Y102" s="6">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="Z102" s="6">
+        <v>0.14999999999999999</v>
+      </c>
+      <c r="AA102" s="8">
+        <v>7.5999999999999996</v>
+      </c>
+      <c r="AB102" s="8">
+        <v>9.5666666666666664</v>
+      </c>
       <c r="AC102" s="8"/>
-      <c r="AD102" s="8"/>
-      <c r="AE102" s="6"/>
+      <c r="AD102" s="8">
+        <v>24.009999999999998</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>0.25</v>
+      </c>
       <c r="AF102" s="9"/>
-      <c r="AG102" s="5"/>
+      <c r="AG102" s="5">
+        <v>0</v>
+      </c>
       <c r="AH102" s="10">
         <v>2</v>
       </c>
@@ -16048,7 +16220,9 @@
       <c r="AB118" s="8">
         <v>3.3716700000000004</v>
       </c>
-      <c r="AC118" s="8"/>
+      <c r="AC118" s="8">
+        <v>9.6178190000000008</v>
+      </c>
       <c r="AD118" s="8">
         <v>15.930558333333332</v>
       </c>
@@ -16673,7 +16847,9 @@
       <c r="AB123" s="8">
         <v>6.9092583333333337</v>
       </c>
-      <c r="AC123" s="8"/>
+      <c r="AC123" s="8">
+        <v>10.412499</v>
+      </c>
       <c r="AD123" s="8">
         <v>18.361575000000002</v>
       </c>
@@ -16916,7 +17092,7 @@
         <v>0.038105709462129794</v>
       </c>
       <c r="W125" s="6">
-        <v>0.014373876439221821</v>
+        <v>0.01472753841133826</v>
       </c>
       <c r="X125" s="8">
         <v>29.757857142857144</v>
@@ -17064,7 +17240,9 @@
       <c r="AB126" s="8">
         <v>9.8886680000000009</v>
       </c>
-      <c r="AC126" s="8"/>
+      <c r="AC126" s="8">
+        <v>14.547332000000001</v>
+      </c>
       <c r="AD126" s="8">
         <v>21.495331999999998</v>
       </c>
@@ -19078,7 +19256,9 @@
       <c r="AB142" s="8">
         <v>4.3063735294117649</v>
       </c>
-      <c r="AC142" s="8"/>
+      <c r="AC142" s="8">
+        <v>8.9692290000000003</v>
+      </c>
       <c r="AD142" s="8">
         <v>17.645237142857145</v>
       </c>
@@ -19467,7 +19647,9 @@
       <c r="AB145" s="8">
         <v>4.2243615384615385</v>
       </c>
-      <c r="AC145" s="8"/>
+      <c r="AC145" s="8">
+        <v>7.6349640000000001</v>
+      </c>
       <c r="AD145" s="8">
         <v>11.593652380952381</v>
       </c>
@@ -19727,7 +19909,9 @@
       <c r="AB147" s="8">
         <v>2.6285714285714286</v>
       </c>
-      <c r="AC147" s="8"/>
+      <c r="AC147" s="8">
+        <v>6.8999990000000002</v>
+      </c>
       <c r="AD147" s="8">
         <v>13.853176190476191</v>
       </c>
@@ -20610,7 +20794,9 @@
       <c r="AB154" s="8">
         <v>10.053846153846154</v>
       </c>
-      <c r="AC154" s="8"/>
+      <c r="AC154" s="8">
+        <v>21.049084000000001</v>
+      </c>
       <c r="AD154" s="8">
         <v>28.988092857142856</v>
       </c>
@@ -21299,7 +21485,7 @@
         <v>0.077095556429414083</v>
       </c>
       <c r="W160" s="6">
-        <v>0.021594180102241449</v>
+        <v>0.020965001966181677</v>
       </c>
       <c r="X160" s="8">
         <v>31.628335</v>
@@ -21562,7 +21748,9 @@
       <c r="AB162" s="8">
         <v>3.009647368421053</v>
       </c>
-      <c r="AC162" s="8"/>
+      <c r="AC162" s="8">
+        <v>14.506315000000001</v>
+      </c>
       <c r="AD162" s="8">
         <v>22.233335</v>
       </c>
@@ -22048,7 +22236,9 @@
       <c r="AB166" s="8">
         <v>5.2243615384615385</v>
       </c>
-      <c r="AC166" s="8"/>
+      <c r="AC166" s="8">
+        <v>7.9999989999999999</v>
+      </c>
       <c r="AD166" s="8">
         <v>14.955130769230768</v>
       </c>
@@ -22570,7 +22760,9 @@
       <c r="AB170" s="8">
         <v>3.5223800000000001</v>
       </c>
-      <c r="AC170" s="8"/>
+      <c r="AC170" s="8">
+        <v>10.02238</v>
+      </c>
       <c r="AD170" s="8">
         <v>16.970477142857142</v>
       </c>
@@ -22699,7 +22891,9 @@
       <c r="AB171" s="8">
         <v>5.5224652173913045</v>
       </c>
-      <c r="AC171" s="8"/>
+      <c r="AC171" s="8">
+        <v>9.5929749999999991</v>
+      </c>
       <c r="AD171" s="8">
         <v>15.287655555555556</v>
       </c>
@@ -23066,7 +23260,9 @@
       <c r="AB174" s="8">
         <v>2.7768108695652174</v>
       </c>
-      <c r="AC174" s="8"/>
+      <c r="AC174" s="8">
+        <v>10.114492</v>
+      </c>
       <c r="AD174" s="8">
         <v>17.070289130434784</v>
       </c>
@@ -23195,7 +23391,9 @@
       <c r="AB175" s="8">
         <v>8.5753952380952381</v>
       </c>
-      <c r="AC175" s="8"/>
+      <c r="AC175" s="8">
+        <v>15.212697</v>
+      </c>
       <c r="AD175" s="8">
         <v>22.162700000000001</v>
       </c>
@@ -23842,7 +24040,9 @@
       <c r="AB180" s="8">
         <v>28.0666625</v>
       </c>
-      <c r="AC180" s="8"/>
+      <c r="AC180" s="8">
+        <v>35.570832000000003</v>
+      </c>
       <c r="AD180" s="8">
         <v>43.516662500000002</v>
       </c>
@@ -23971,7 +24171,9 @@
       <c r="AB181" s="8">
         <v>1.1230769230769231</v>
       </c>
-      <c r="AC181" s="8"/>
+      <c r="AC181" s="8">
+        <v>5.438701</v>
+      </c>
       <c r="AD181" s="8">
         <v>12.89270625</v>
       </c>
@@ -24586,7 +24788,9 @@
       <c r="AB186" s="8">
         <v>7.6154785714285707</v>
       </c>
-      <c r="AC186" s="8"/>
+      <c r="AC186" s="8">
+        <v>13.656101</v>
+      </c>
       <c r="AD186" s="8">
         <v>19.231249999999999</v>
       </c>
@@ -24715,7 +24919,9 @@
       <c r="AB187" s="8">
         <v>12.796428571428573</v>
       </c>
-      <c r="AC187" s="8"/>
+      <c r="AC187" s="8">
+        <v>24.713094000000002</v>
+      </c>
       <c r="AD187" s="8">
         <v>30.444446666666668</v>
       </c>
@@ -24977,7 +25183,9 @@
       <c r="AB189" s="8">
         <v>10.615306122448979</v>
       </c>
-      <c r="AC189" s="8"/>
+      <c r="AC189" s="8">
+        <v>14.822639000000001</v>
+      </c>
       <c r="AD189" s="8">
         <v>21.326334000000003</v>
       </c>
@@ -25106,7 +25314,9 @@
       <c r="AB190" s="8">
         <v>5.9406249999999998</v>
       </c>
-      <c r="AC190" s="8"/>
+      <c r="AC190" s="8">
+        <v>8.9616769999999999</v>
+      </c>
       <c r="AD190" s="8">
         <v>14.535963157894736</v>
       </c>
@@ -25679,7 +25889,7 @@
         <v>19944</v>
       </c>
       <c r="B195" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C195" s="4">
         <v>44</v>
@@ -25715,25 +25925,59 @@
       <c t="s" r="N195" s="4">
         <v>52</v>
       </c>
-      <c r="O195" s="5"/>
-      <c r="P195" s="5"/>
-      <c r="Q195" s="6"/>
-      <c r="R195" s="7"/>
-      <c r="S195" s="6"/>
-      <c r="T195" s="6"/>
-      <c r="U195" s="6"/>
-      <c r="V195" s="6"/>
-      <c r="W195" s="6"/>
-      <c r="X195" s="8"/>
-      <c r="Y195" s="6"/>
-      <c r="Z195" s="6"/>
-      <c r="AA195" s="8"/>
-      <c r="AB195" s="8"/>
+      <c r="O195" s="5">
+        <v>4884.4300000000003</v>
+      </c>
+      <c r="P195" s="5">
+        <v>4884.4300000000003</v>
+      </c>
+      <c r="Q195" s="6">
+        <v>0.10615078017075441</v>
+      </c>
+      <c r="R195" s="7">
+        <v>55</v>
+      </c>
+      <c r="S195" s="6">
+        <v>-0.017857142857142905</v>
+      </c>
+      <c r="T195" s="6">
+        <v>0.2094501303120323</v>
+      </c>
+      <c r="U195" s="6">
+        <v>-0.12056995391478635</v>
+      </c>
+      <c r="V195" s="6">
+        <v>0.02361288830017013</v>
+      </c>
+      <c r="W195" s="6">
+        <v>-0.0022058868690921969</v>
+      </c>
+      <c r="X195" s="8">
+        <v>28.364493478260869</v>
+      </c>
+      <c r="Y195" s="6">
+        <v>0.34782608695652173</v>
+      </c>
+      <c r="Z195" s="6">
+        <v>0.021739130434782608</v>
+      </c>
+      <c r="AA195" s="8">
+        <v>5.1455134615384619</v>
+      </c>
+      <c r="AB195" s="8">
+        <v>8.3365934782608697</v>
+      </c>
       <c r="AC195" s="8"/>
-      <c r="AD195" s="8"/>
-      <c r="AE195" s="6"/>
+      <c r="AD195" s="8">
+        <v>20.392028260869566</v>
+      </c>
+      <c r="AE195" s="6">
+        <v>0.60869565217391308</v>
+      </c>
       <c r="AF195" s="9"/>
-      <c r="AG195" s="5"/>
+      <c r="AG195" s="5">
+        <v>-53.399999999999999</v>
+      </c>
       <c r="AH195" s="10">
         <v>2</v>
       </c>
@@ -26245,7 +26489,9 @@
       <c r="AB199" s="8">
         <v>3.7350000000000003</v>
       </c>
-      <c r="AC199" s="8"/>
+      <c r="AC199" s="8">
+        <v>12.515000000000001</v>
+      </c>
       <c r="AD199" s="8">
         <v>19.45833</v>
       </c>
@@ -26374,7 +26620,9 @@
       <c r="AB200" s="8">
         <v>3.5738142857142856</v>
       </c>
-      <c r="AC200" s="8"/>
+      <c r="AC200" s="8">
+        <v>8.8142849999999999</v>
+      </c>
       <c r="AD200" s="8">
         <v>15.778571428571428</v>
       </c>
@@ -27074,7 +27322,9 @@
       <c r="AB206" s="8">
         <v>6.6854125</v>
       </c>
-      <c r="AC206" s="8"/>
+      <c r="AC206" s="8">
+        <v>16.391666000000001</v>
+      </c>
       <c r="AD206" s="8">
         <v>23.3041625</v>
       </c>
@@ -27199,7 +27449,9 @@
       <c r="AB207" s="8">
         <v>10.993936363636363</v>
       </c>
-      <c r="AC207" s="8"/>
+      <c r="AC207" s="8">
+        <v>18.363634999999999</v>
+      </c>
       <c r="AD207" s="8">
         <v>25.31060909090909</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-30).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-30).xlsx
@@ -912,66 +912,66 @@
   </si>
   <si>
     <t>214
-171</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>R$ 834.846,37</t>
-  </si>
-  <si>
-    <t>R$ 4.587,07
-R$ 4.683,23</t>
-  </si>
-  <si>
-    <t>16.1%
-17.9%</t>
-  </si>
-  <si>
-    <t>49.5</t>
-  </si>
-  <si>
-    <t>5.4%</t>
-  </si>
-  <si>
-    <t>(70.0%)</t>
-  </si>
-  <si>
-    <t>(122.1%)</t>
-  </si>
-  <si>
-    <t>4.3%</t>
-  </si>
-  <si>
-    <t>1.0%</t>
-  </si>
-  <si>
-    <t>27.8</t>
-  </si>
-  <si>
-    <t>71.3%</t>
-  </si>
-  <si>
-    <t>11.6%</t>
+174</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>R$ 852.376,62</t>
+  </si>
+  <si>
+    <t>R$ 4.607,44
+R$ 4.703,23</t>
+  </si>
+  <si>
+    <t>16.5%
+18.3%</t>
+  </si>
+  <si>
+    <t>49.6</t>
+  </si>
+  <si>
+    <t>5.7%</t>
+  </si>
+  <si>
+    <t>(64.5%)</t>
+  </si>
+  <si>
+    <t>(116.2%)</t>
+  </si>
+  <si>
+    <t>4.5%</t>
+  </si>
+  <si>
+    <t>1.1%</t>
+  </si>
+  <si>
+    <t>27.7</t>
+  </si>
+  <si>
+    <t>71.5%</t>
+  </si>
+  <si>
+    <t>11.4%</t>
   </si>
   <si>
     <t>5.1</t>
   </si>
   <si>
-    <t>7.5</t>
+    <t>7.4</t>
   </si>
   <si>
     <t>12.5</t>
   </si>
   <si>
-    <t>19.4</t>
-  </si>
-  <si>
-    <t>69.7%</t>
-  </si>
-  <si>
-    <t>-R$ 20.481,73</t>
+    <t>19.3</t>
+  </si>
+  <si>
+    <t>70.1%</t>
+  </si>
+  <si>
+    <t>-R$ 20.725,63</t>
   </si>
   <si>
     <t>2.94</t>
@@ -2066,7 +2066,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>44</v>
@@ -2102,25 +2102,61 @@
       <c t="s" r="N6" s="4">
         <v>52</v>
       </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="6"/>
+      <c r="O6" s="5">
+        <v>10282.6</v>
+      </c>
+      <c r="P6" s="5">
+        <v>10282.6</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>0.57999385371850032</v>
+      </c>
+      <c r="R6" s="7">
+        <v>89</v>
+      </c>
+      <c r="S6" s="6">
+        <v>0.18666666666666676</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0.31289443331453132</v>
+      </c>
+      <c r="U6" s="6">
+        <v>-0.0087868535195378596</v>
+      </c>
+      <c r="V6" s="6">
+        <v>0.085591980627467756</v>
+      </c>
+      <c r="W6" s="6">
+        <v>0.050567764962169102</v>
+      </c>
+      <c r="X6" s="8">
+        <v>25.294064383561643</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>0.9452054794520548</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>8.6271313953488384</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>3.1025458333333331</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>11.900034</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>18.767579452054797</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>0.80821917808219179</v>
+      </c>
       <c r="AF6" s="9"/>
-      <c r="AG6" s="5"/>
+      <c r="AG6" s="5">
+        <v>0</v>
+      </c>
       <c r="AH6" s="10">
         <v>5</v>
       </c>
@@ -4876,7 +4912,7 @@
         <v>19546</v>
       </c>
       <c r="B28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C28" s="4">
         <v>44</v>
@@ -4912,25 +4948,61 @@
       <c t="s" r="N28" s="4">
         <v>52</v>
       </c>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="7"/>
-      <c r="S28" s="6"/>
-      <c r="T28" s="6"/>
-      <c r="U28" s="6"/>
-      <c r="V28" s="6"/>
-      <c r="W28" s="6"/>
-      <c r="X28" s="8"/>
-      <c r="Y28" s="6"/>
-      <c r="Z28" s="6"/>
-      <c r="AA28" s="8"/>
-      <c r="AB28" s="8"/>
-      <c r="AC28" s="8"/>
-      <c r="AD28" s="8"/>
-      <c r="AE28" s="6"/>
+      <c r="O28" s="5">
+        <v>4054.54</v>
+      </c>
+      <c r="P28" s="5">
+        <v>4054.54</v>
+      </c>
+      <c r="Q28" s="6">
+        <v>0.2482651609844404</v>
+      </c>
+      <c r="R28" s="7">
+        <v>48</v>
+      </c>
+      <c r="S28" s="6">
+        <v>0.1707317073170731</v>
+      </c>
+      <c r="T28" s="6">
+        <v>0.00032072688887025411</v>
+      </c>
+      <c r="U28" s="6">
+        <v>-0.33470864759010888</v>
+      </c>
+      <c r="V28" s="6">
+        <v>0.10781654638997272</v>
+      </c>
+      <c r="W28" s="6">
+        <v>0.094914959526851389</v>
+      </c>
+      <c r="X28" s="8">
+        <v>21.991109999999999</v>
+      </c>
+      <c r="Y28" s="6">
+        <v>0.59999999999999998</v>
+      </c>
+      <c r="Z28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="8">
+        <v>3.3130000000000002</v>
+      </c>
+      <c r="AB28" s="8">
+        <v>6.0222233333333328</v>
+      </c>
+      <c r="AC28" s="8">
+        <v>8.7980280000000004</v>
+      </c>
+      <c r="AD28" s="8">
+        <v>15.818333333333333</v>
+      </c>
+      <c r="AE28" s="6">
+        <v>1</v>
+      </c>
       <c r="AF28" s="9"/>
-      <c r="AG28" s="5"/>
+      <c r="AG28" s="5">
+        <v>-243.90000000000001</v>
+      </c>
       <c r="AH28" s="10">
         <v>2</v>
       </c>
@@ -5930,7 +6002,9 @@
       <c r="AB36" s="8">
         <v>18.210604545454547</v>
       </c>
-      <c r="AC36" s="8"/>
+      <c r="AC36" s="8">
+        <v>26.231294999999999</v>
+      </c>
       <c r="AD36" s="8">
         <v>29.900642307692308</v>
       </c>
@@ -12739,7 +12813,7 @@
         <v>0.10675258687627233</v>
       </c>
       <c r="W90" s="6">
-        <v>0.069290837033678498</v>
+        <v>0.070144409832424384</v>
       </c>
       <c r="X90" s="8">
         <v>66.171667499999998</v>
@@ -14284,7 +14358,9 @@
       <c r="AB102" s="8">
         <v>9.5666666666666664</v>
       </c>
-      <c r="AC102" s="8"/>
+      <c r="AC102" s="8">
+        <v>17.942062</v>
+      </c>
       <c r="AD102" s="8">
         <v>24.009999999999998</v>
       </c>
@@ -19621,10 +19697,10 @@
         <v>0.375</v>
       </c>
       <c r="T145" s="6">
-        <v>-13.231760837670731</v>
+        <v>-0.01303376183323436</v>
       </c>
       <c r="U145" s="6">
-        <v>-13.586622506724423</v>
+        <v>-0.36789543088692495</v>
       </c>
       <c r="V145" s="6">
         <v>0.051207339225206976</v>
@@ -21202,7 +21278,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>44</v>
@@ -21238,25 +21314,61 @@
       <c t="s" r="N158" s="4">
         <v>52</v>
       </c>
-      <c r="O158" s="5"/>
-      <c r="P158" s="5"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="6"/>
-      <c r="T158" s="6"/>
-      <c r="U158" s="6"/>
-      <c r="V158" s="6"/>
-      <c r="W158" s="6"/>
-      <c r="X158" s="8"/>
-      <c r="Y158" s="6"/>
-      <c r="Z158" s="6"/>
-      <c r="AA158" s="8"/>
-      <c r="AB158" s="8"/>
-      <c r="AC158" s="8"/>
-      <c r="AD158" s="8"/>
-      <c r="AE158" s="6"/>
+      <c r="O158" s="5">
+        <v>3193.1100000000001</v>
+      </c>
+      <c r="P158" s="5">
+        <v>3193.1100000000001</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>0.14689275682975733</v>
+      </c>
+      <c r="R158" s="7">
+        <v>32</v>
+      </c>
+      <c r="S158" s="6">
+        <v>0.18518518518518512</v>
+      </c>
+      <c r="T158" s="6">
+        <v>0.35449442706327056</v>
+      </c>
+      <c r="U158" s="6">
+        <v>0.033174460009207325</v>
+      </c>
+      <c r="V158" s="6">
+        <v>0.10923410092355101</v>
+      </c>
+      <c r="W158" s="6">
+        <v>0.069564311909079232</v>
+      </c>
+      <c r="X158" s="8">
+        <v>25.167857142857144</v>
+      </c>
+      <c r="Y158" s="6">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="Z158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="8">
+        <v>4.7929303030303032</v>
+      </c>
+      <c r="AB158" s="8">
+        <v>1.9095250000000001</v>
+      </c>
+      <c r="AC158" s="8">
+        <v>6.8049249999999999</v>
+      </c>
+      <c r="AD158" s="8">
+        <v>13.741667857142858</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0.8928571428571429</v>
+      </c>
       <c r="AF158" s="9"/>
-      <c r="AG158" s="5"/>
+      <c r="AG158" s="5">
+        <v>0</v>
+      </c>
       <c r="AH158" s="10">
         <v>2</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-30).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-30).xlsx
@@ -911,55 +911,58 @@
     <t>GUIMARAES FRAGA,MARESSA</t>
   </si>
   <si>
-    <t>214
-174</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>R$ 852.376,62</t>
-  </si>
-  <si>
-    <t>R$ 4.607,44
-R$ 4.703,23</t>
-  </si>
-  <si>
-    <t>16.5%
-18.3%</t>
-  </si>
-  <si>
-    <t>49.6</t>
-  </si>
-  <si>
-    <t>5.7%</t>
-  </si>
-  <si>
-    <t>(64.5%)</t>
-  </si>
-  <si>
-    <t>(116.2%)</t>
+    <t>DE LOURDES RAMOS,MARIA</t>
+  </si>
+  <si>
+    <t>215
+176</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>R$ 861.795,45</t>
+  </si>
+  <si>
+    <t>R$ 4.608,53
+R$ 4.703,30</t>
+  </si>
+  <si>
+    <t>16.2%
+18.0%</t>
+  </si>
+  <si>
+    <t>49.7</t>
+  </si>
+  <si>
+    <t>5.4%</t>
+  </si>
+  <si>
+    <t>(63.2%)</t>
+  </si>
+  <si>
+    <t>(114.6%)</t>
   </si>
   <si>
     <t>4.5%</t>
   </si>
   <si>
-    <t>1.1%</t>
-  </si>
-  <si>
-    <t>27.7</t>
+    <t>1.2%</t>
+  </si>
+  <si>
+    <t>27.6</t>
   </si>
   <si>
     <t>71.5%</t>
   </si>
   <si>
-    <t>11.4%</t>
+    <t>11.3%</t>
   </si>
   <si>
     <t>5.1</t>
   </si>
   <si>
-    <t>7.4</t>
+    <t>7.3</t>
   </si>
   <si>
     <t>12.5</t>
@@ -968,7 +971,7 @@
     <t>19.3</t>
   </si>
   <si>
-    <t>70.1%</t>
+    <t>70.4%</t>
   </si>
   <si>
     <t>-R$ 20.725,63</t>
@@ -5694,7 +5697,7 @@
         <v>19560</v>
       </c>
       <c r="B34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C34" s="4">
         <v>44</v>
@@ -5730,25 +5733,61 @@
       <c t="s" r="N34" s="4">
         <v>52</v>
       </c>
-      <c r="O34" s="5"/>
-      <c r="P34" s="5"/>
-      <c r="Q34" s="6"/>
-      <c r="R34" s="7"/>
-      <c r="S34" s="6"/>
-      <c r="T34" s="6"/>
-      <c r="U34" s="6"/>
-      <c r="V34" s="6"/>
-      <c r="W34" s="6"/>
-      <c r="X34" s="8"/>
-      <c r="Y34" s="6"/>
-      <c r="Z34" s="6"/>
-      <c r="AA34" s="8"/>
-      <c r="AB34" s="8"/>
-      <c r="AC34" s="8"/>
-      <c r="AD34" s="8"/>
-      <c r="AE34" s="6"/>
+      <c r="O34" s="5">
+        <v>6580.4099999999999</v>
+      </c>
+      <c r="P34" s="5">
+        <v>6580.4099999999999</v>
+      </c>
+      <c r="Q34" s="6">
+        <v>-0.17946726053907391</v>
+      </c>
+      <c r="R34" s="7">
+        <v>79</v>
+      </c>
+      <c r="S34" s="6">
+        <v>-0.25471698113207553</v>
+      </c>
+      <c r="T34" s="6">
+        <v>0.63735957181999303</v>
+      </c>
+      <c r="U34" s="6">
+        <v>0.30428914003838664</v>
+      </c>
+      <c r="V34" s="6">
+        <v>0.1145824500297094</v>
+      </c>
+      <c r="W34" s="6">
+        <v>0.074885835381078084</v>
+      </c>
+      <c r="X34" s="8">
+        <v>20.812244897959182</v>
+      </c>
+      <c r="Y34" s="6">
+        <v>0.63265306122448983</v>
+      </c>
+      <c r="Z34" s="6">
+        <v>0.040816326530612242</v>
+      </c>
+      <c r="AA34" s="8">
+        <v>7.1967948717948724</v>
+      </c>
+      <c r="AB34" s="8">
+        <v>2.8775510204081631</v>
+      </c>
+      <c r="AC34" s="8">
+        <v>10.310544</v>
+      </c>
+      <c r="AD34" s="8">
+        <v>16.255442857142857</v>
+      </c>
+      <c r="AE34" s="6">
+        <v>0.91836734693877553</v>
+      </c>
       <c r="AF34" s="9"/>
-      <c r="AG34" s="5"/>
+      <c r="AG34" s="5">
+        <v>0</v>
+      </c>
       <c r="AH34" s="10">
         <v>4</v>
       </c>
@@ -16042,7 +16081,9 @@
       <c r="Z116" s="6"/>
       <c r="AA116" s="8"/>
       <c r="AB116" s="8"/>
-      <c r="AC116" s="8"/>
+      <c r="AC116" s="8">
+        <v>14.328556000000001</v>
+      </c>
       <c r="AD116" s="8"/>
       <c r="AE116" s="6"/>
       <c r="AF116" s="9"/>
@@ -19159,7 +19200,7 @@
         <v>19793</v>
       </c>
       <c r="B141" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C141" s="4">
         <v>44</v>
@@ -19195,25 +19236,61 @@
       <c t="s" r="N141" s="4">
         <v>52</v>
       </c>
-      <c r="O141" s="5"/>
-      <c r="P141" s="5"/>
-      <c r="Q141" s="6"/>
-      <c r="R141" s="7"/>
-      <c r="S141" s="6"/>
-      <c r="T141" s="6"/>
-      <c r="U141" s="6"/>
-      <c r="V141" s="6"/>
-      <c r="W141" s="6"/>
-      <c r="X141" s="8"/>
-      <c r="Y141" s="6"/>
-      <c r="Z141" s="6"/>
-      <c r="AA141" s="8"/>
-      <c r="AB141" s="8"/>
-      <c r="AC141" s="8"/>
-      <c r="AD141" s="8"/>
-      <c r="AE141" s="6"/>
+      <c r="O141" s="5">
+        <v>2838.4200000000001</v>
+      </c>
+      <c r="P141" s="5">
+        <v>2838.4200000000001</v>
+      </c>
+      <c r="Q141" s="6">
+        <v>0.56135583524027455</v>
+      </c>
+      <c r="R141" s="7">
+        <v>36</v>
+      </c>
+      <c r="S141" s="6">
+        <v>0.43999999999999995</v>
+      </c>
+      <c r="T141" s="6">
+        <v>0.42153412814171265</v>
+      </c>
+      <c r="U141" s="6">
+        <v>0.086992376040191374</v>
+      </c>
+      <c r="V141" s="6">
+        <v>0.14767053501595959</v>
+      </c>
+      <c r="W141" s="6">
+        <v>0.07967143692617723</v>
+      </c>
+      <c r="X141" s="8">
+        <v>19.509164999999999</v>
+      </c>
+      <c r="Y141" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA141" s="8">
+        <v>3.9264705882352939</v>
+      </c>
+      <c r="AB141" s="8">
+        <v>1.661111111111111</v>
+      </c>
+      <c r="AC141" s="8">
+        <v>5.4161109999999999</v>
+      </c>
+      <c r="AD141" s="8">
+        <v>12.643335</v>
+      </c>
+      <c r="AE141" s="6">
+        <v>1</v>
+      </c>
       <c r="AF141" s="9"/>
-      <c r="AG141" s="5"/>
+      <c r="AG141" s="5">
+        <v>0</v>
+      </c>
       <c r="AH141" s="10">
         <v>4</v>
       </c>
@@ -26079,7 +26156,9 @@
       <c r="AB195" s="8">
         <v>8.3365934782608697</v>
       </c>
-      <c r="AC195" s="8"/>
+      <c r="AC195" s="8">
+        <v>13.471014</v>
+      </c>
       <c r="AD195" s="8">
         <v>20.392028260869566</v>
       </c>
@@ -28413,112 +28492,203 @@
         <v>56</v>
       </c>
     </row>
-    <row r="216" ht="24.75" customHeight="1">
-      <c t="s" r="A216" s="14">
+    <row r="216" ht="13.5" customHeight="1">
+      <c r="A216" s="2">
+        <v>19980</v>
+      </c>
+      <c r="B216" s="3">
+        <v>-1</v>
+      </c>
+      <c t="s" r="C216" s="4">
+        <v>44</v>
+      </c>
+      <c t="s" r="D216" s="4">
+        <v>45</v>
+      </c>
+      <c t="s" r="E216" s="4">
+        <v>46</v>
+      </c>
+      <c t="s" r="F216" s="4">
+        <v>47</v>
+      </c>
+      <c t="s" r="G216" s="4">
+        <v>48</v>
+      </c>
+      <c t="s" r="H216" s="4">
+        <v>49</v>
+      </c>
+      <c t="s" r="I216" s="4">
+        <v>50</v>
+      </c>
+      <c t="s" r="J216" s="4">
+        <v>47</v>
+      </c>
+      <c t="s" r="K216" s="4">
+        <v>51</v>
+      </c>
+      <c t="s" r="L216" s="4">
+        <v>51</v>
+      </c>
+      <c r="M216" s="4"/>
+      <c t="s" r="N216" s="4">
+        <v>52</v>
+      </c>
+      <c r="O216" s="5"/>
+      <c r="P216" s="5"/>
+      <c r="Q216" s="6"/>
+      <c r="R216" s="7"/>
+      <c r="S216" s="6"/>
+      <c r="T216" s="6"/>
+      <c r="U216" s="6"/>
+      <c r="V216" s="6"/>
+      <c r="W216" s="6"/>
+      <c r="X216" s="8"/>
+      <c r="Y216" s="6"/>
+      <c r="Z216" s="6"/>
+      <c r="AA216" s="8"/>
+      <c r="AB216" s="8"/>
+      <c r="AC216" s="8"/>
+      <c r="AD216" s="8"/>
+      <c r="AE216" s="6"/>
+      <c r="AF216" s="9"/>
+      <c r="AG216" s="5"/>
+      <c r="AH216" s="10"/>
+      <c r="AI216" s="11"/>
+      <c r="AJ216" s="12"/>
+      <c t="s" r="AK216" s="4">
+        <v>52</v>
+      </c>
+      <c t="s" r="AL216" s="4">
+        <v>52</v>
+      </c>
+      <c r="AM216" s="2">
+        <v>1</v>
+      </c>
+      <c r="AN216" s="2">
+        <v>1</v>
+      </c>
+      <c t="s" r="AO216" s="4">
+        <v>53</v>
+      </c>
+      <c t="s" r="AP216" s="4">
+        <v>54</v>
+      </c>
+      <c t="s" r="AQ216" s="4">
+        <v>55</v>
+      </c>
+      <c t="s" r="AR216" s="4">
         <v>300</v>
       </c>
-      <c t="s" r="B216" s="14">
+      <c t="s" r="AS216" s="4">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="217" ht="24.75" customHeight="1">
+      <c t="s" r="A217" s="14">
         <v>301</v>
       </c>
-      <c r="C216" s="15"/>
-      <c r="D216" s="15"/>
-      <c r="E216" s="15"/>
-      <c r="F216" s="15"/>
-      <c r="G216" s="15"/>
-      <c r="H216" s="15"/>
-      <c r="I216" s="15"/>
-      <c r="J216" s="15"/>
-      <c r="K216" s="15"/>
-      <c r="L216" s="15"/>
-      <c r="M216" s="15"/>
-      <c t="s" r="N216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="O216" s="14">
+      <c t="s" r="B217" s="14">
         <v>302</v>
       </c>
-      <c t="s" r="P216" s="14">
+      <c r="C217" s="15"/>
+      <c r="D217" s="15"/>
+      <c r="E217" s="15"/>
+      <c r="F217" s="15"/>
+      <c r="G217" s="15"/>
+      <c r="H217" s="15"/>
+      <c r="I217" s="15"/>
+      <c r="J217" s="15"/>
+      <c r="K217" s="15"/>
+      <c r="L217" s="15"/>
+      <c r="M217" s="15"/>
+      <c t="s" r="N217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="O217" s="14">
         <v>303</v>
       </c>
-      <c t="s" r="Q216" s="14">
+      <c t="s" r="P217" s="14">
         <v>304</v>
       </c>
-      <c t="s" r="R216" s="14">
+      <c t="s" r="Q217" s="14">
         <v>305</v>
       </c>
-      <c t="s" r="S216" s="14">
+      <c t="s" r="R217" s="14">
         <v>306</v>
       </c>
-      <c t="s" r="T216" s="14">
+      <c t="s" r="S217" s="14">
         <v>307</v>
       </c>
-      <c t="s" r="U216" s="14">
+      <c t="s" r="T217" s="14">
         <v>308</v>
       </c>
-      <c t="s" r="V216" s="14">
+      <c t="s" r="U217" s="14">
         <v>309</v>
       </c>
-      <c t="s" r="W216" s="14">
+      <c t="s" r="V217" s="14">
         <v>310</v>
       </c>
-      <c t="s" r="X216" s="14">
+      <c t="s" r="W217" s="14">
         <v>311</v>
       </c>
-      <c t="s" r="Y216" s="14">
+      <c t="s" r="X217" s="14">
         <v>312</v>
       </c>
-      <c t="s" r="Z216" s="14">
+      <c t="s" r="Y217" s="14">
         <v>313</v>
       </c>
-      <c t="s" r="AA216" s="14">
+      <c t="s" r="Z217" s="14">
         <v>314</v>
       </c>
-      <c t="s" r="AB216" s="14">
+      <c t="s" r="AA217" s="14">
         <v>315</v>
       </c>
-      <c t="s" r="AC216" s="14">
+      <c t="s" r="AB217" s="14">
         <v>316</v>
       </c>
-      <c t="s" r="AD216" s="14">
+      <c t="s" r="AC217" s="14">
         <v>317</v>
       </c>
-      <c t="s" r="AE216" s="14">
+      <c t="s" r="AD217" s="14">
         <v>318</v>
       </c>
-      <c r="AF216" s="14"/>
-      <c t="s" r="AG216" s="14">
+      <c t="s" r="AE217" s="14">
         <v>319</v>
       </c>
-      <c t="s" r="AH216" s="14">
+      <c r="AF217" s="14"/>
+      <c t="s" r="AG217" s="14">
         <v>320</v>
       </c>
-      <c t="s" r="AI216" s="14">
+      <c t="s" r="AH217" s="14">
         <v>321</v>
       </c>
-      <c r="AJ216" s="15"/>
-      <c t="s" r="AK216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="AL216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="AM216" s="14">
+      <c t="s" r="AI217" s="14">
         <v>322</v>
       </c>
-      <c t="s" r="AN216" s="14">
-        <v>322</v>
-      </c>
-      <c r="AO216" s="15"/>
-      <c r="AP216" s="15"/>
-      <c r="AQ216" s="15"/>
-      <c r="AR216" s="15"/>
-      <c r="AS216" s="15"/>
+      <c r="AJ217" s="15"/>
+      <c t="s" r="AK217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="AL217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="AM217" s="14">
+        <v>323</v>
+      </c>
+      <c t="s" r="AN217" s="14">
+        <v>323</v>
+      </c>
+      <c r="AO217" s="15"/>
+      <c r="AP217" s="15"/>
+      <c r="AQ217" s="15"/>
+      <c r="AR217" s="15"/>
+      <c r="AS217" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AS216" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:AS217" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>